--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -417,17 +417,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V11"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="47" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>위헬스 장산역점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>wehealthjangsan@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1800-8273</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 세실로 45 2층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/wehealth_jangsan</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>230</v>
+        <v>425</v>
       </c>
       <c r="Q2" t="n">
-        <v>536</v>
+        <v>978</v>
       </c>
       <c r="R2" t="n">
-        <v>766</v>
+        <v>1403</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1867376356</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1867376356</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>425</v>
+        <v>1459</v>
       </c>
       <c r="Q3" t="n">
-        <v>977</v>
+        <v>1390</v>
       </c>
       <c r="R3" t="n">
-        <v>1402</v>
+        <v>2849</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -747,34 +747,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>멋짐 헬스 &amp; PT 마린시티점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>mutgym_@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1380-2436</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://blog.naver.com/mutgym_</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -809,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1459</v>
+        <v>71</v>
       </c>
       <c r="Q4" t="n">
-        <v>1387</v>
+        <v>202</v>
       </c>
       <c r="R4" t="n">
-        <v>2846</v>
+        <v>273</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>2055602485</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/2055602485</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,39 +841,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>멋짐 헬스 &amp; PT 마린시티점</t>
+          <t>올바른운동 해운대좌동점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mutgym_@naver.com</t>
+          <t>yesmyt@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1380-2436</t>
+          <t>0507-1391-3259</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산광역시 해운대구 좌동순환로 181 5층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mutgym_</t>
+          <t>https://abrtraining.kr/</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>70</v>
+        <v>278</v>
       </c>
       <c r="Q5" t="n">
-        <v>202</v>
+        <v>605</v>
       </c>
       <c r="R5" t="n">
-        <v>272</v>
+        <v>883</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2055602485</t>
+          <t>1715982137</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2055602485</t>
+          <t>https://m.place.naver.com/place/1715982137</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,39 +935,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>올바른운동 해운대좌동점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>yesmyt@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1391-3259</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 좌동순환로 181 5층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://abrtraining.kr/</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -997,13 +997,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>278</v>
+        <v>475</v>
       </c>
       <c r="Q6" t="n">
-        <v>612</v>
+        <v>149</v>
       </c>
       <c r="R6" t="n">
-        <v>890</v>
+        <v>624</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1715982137</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1715982137</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1029,39 +1029,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>핏 라이프스타일 해운대</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>tmzjwl27@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0507-1397-0149</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 세실로69번길 15 7F 핏 라이프스타일</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://drive.google.com/drive/folders/1FE2ojnmHyYiv3OlukWegw9jtzBYKObAA</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1067,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1087,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>475</v>
+        <v>403</v>
       </c>
       <c r="Q7" t="n">
-        <v>149</v>
+        <v>1057</v>
       </c>
       <c r="R7" t="n">
-        <v>624</v>
+        <v>1460</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1102,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1236047384</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1236047384</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,34 +1119,34 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>모션업PT 체형관리센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>motionuppt2879@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1362-1057</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산광역시 해운대구 좌동순환로 506 영풍리젠시 403호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/motionuppt2879</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,7 +1161,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1176,7 +1172,7 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1181,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2067</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>2141</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1196,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1186141561</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1186141561</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,39 +1213,39 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>리커버리 스트레칭 센텀시티점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>recovery_stretching@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>051-746-0168</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산광역시 해운대구 센텀3로 32 트럼프월드 센텀2 B1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://www.recoverystretching.com/</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1279,13 +1275,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>297</v>
+        <v>492</v>
       </c>
       <c r="Q9" t="n">
-        <v>462</v>
+        <v>683</v>
       </c>
       <c r="R9" t="n">
-        <v>759</v>
+        <v>1175</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1290,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1597605677</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1597605677</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,34 +1307,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>리커버리 스트레칭 마린시티점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>recovery_stretching@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1363-0319</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산광역시 해운대구 마린시티2로 33 B동 7층 735호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/recovery_stretching</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1373,13 +1369,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>48</v>
+        <v>256</v>
       </c>
       <c r="Q10" t="n">
-        <v>266</v>
+        <v>333</v>
       </c>
       <c r="R10" t="n">
-        <v>314</v>
+        <v>589</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1384,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1461885327</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1461885327</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1405,39 +1401,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠,오락</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>24시 트렌드핏 피트니스 해운대점 헬스&amp;PT</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>trendfit_haeundae@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1493-4890</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 좌동순환로 245 4층</t>
+          <t>부산광역시 해운대구 해운대로 650 2층 214, 215호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://open.kakao.com/o/gzRIcJqf</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1447,7 +1443,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1458,7 +1454,7 @@
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1467,13 +1463,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>498</v>
+        <v>445</v>
       </c>
       <c r="Q11" t="n">
-        <v>590</v>
+        <v>982</v>
       </c>
       <c r="R11" t="n">
-        <v>1088</v>
+        <v>1427</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,15 +1478,955 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1802178838</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1802178838</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>헬짐 헬스&amp;PT 센텀시티점</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hellgym_centum@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1494-3739</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hellgym_centum</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>460</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1235</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1695</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1986332432</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1986332432</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>겟바디핏 PT 해운대점</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>charles-9@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1468-1626</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 중동2로34번길 10 3층 겟바디핏</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/charles-9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>312</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1419</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1731</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1949181378</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1949181378</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>우디짐PT</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>woodygym@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-8691-1998</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 87 6층 우디짐</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/woodygym</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>351</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>374</v>
+      </c>
+      <c r="R14" t="n">
+        <v>725</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1696092453</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1696092453</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>더플래닛짐 헬스&amp;PT 해운대 장산역점</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>theplanetgym@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0507-1310-5564</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 77 성부빌딩 8층</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1992573620</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>191</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>273</v>
+      </c>
+      <c r="R15" t="n">
+        <v>464</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1992573620</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1992573620</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>지온피트니스 PT &amp; 필라테스</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>shopin_korea@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0507-1305-3103</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티2로 33 해운대두산위브더제니스 B타워 5층</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>https://zionfitness.net</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>237</v>
+      </c>
+      <c r="R16" t="n">
+        <v>287</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>322480233</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/322480233</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>위헬스 장산역점</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>wehealthjangsan@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1800-8273</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 세실로 45 2층</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>https://smartstore.naver.com/wehealth_jangsan</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>230</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>537</v>
+      </c>
+      <c r="R17" t="n">
+        <v>767</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1867376356</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1867376356</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>브론즈짐</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>busan_dpksj@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0507-1362-7008</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 중동2로 16 해운대온천센터 7층</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bronzegym_haeundae/</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>354</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>284</v>
+      </c>
+      <c r="R18" t="n">
+        <v>638</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1882702233</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1882702233</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>팬덤핏 PT 마린시티점</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>fandomfit@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0507-1302-3167</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티3로 39 205호</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fandomfit_marinecity</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>206</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>393</v>
+      </c>
+      <c r="R19" t="n">
+        <v>599</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>1766770335</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1766770335</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>굿웨이 피트니스 헬스&amp;PT</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goodway_fitness@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0507-1319-3991</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 중동1로 15-2 서림빌딩 4층</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>https://open.kakao.com/o/sJsElyXg</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>318</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>298</v>
+      </c>
+      <c r="R20" t="n">
+        <v>616</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1370971185</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1370971185</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>스포츠,오락</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>솔레노어 PT 부티크 마린시티점</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>soleilnoir_ptstudio@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>051-992-1317</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>부산광역시 해운대구 마린시티2로 2 403호,404호</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>https://www.soleilnoir.kr/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>59</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>131</v>
+      </c>
+      <c r="R21" t="n">
+        <v>190</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>1753451686</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1753451686</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -1081,7 +1081,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="Q2" t="n">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="R2" t="n">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>마이애미짐 해운대점 24시헬스PT</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>jeffkim94@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1469-0064</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jeffkim94</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -723,13 +715,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>430</v>
+        <v>476</v>
       </c>
       <c r="Q3" t="n">
-        <v>957</v>
+        <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>1387</v>
+        <v>632</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -738,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1040976831</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1040976831</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -760,29 +752,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>마이애미짐 해운대점 24시헬스PT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>jeffkim94@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1469-0064</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/jeffkim94</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -821,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>476</v>
+        <v>430</v>
       </c>
       <c r="Q4" t="n">
-        <v>156</v>
+        <v>957</v>
       </c>
       <c r="R4" t="n">
-        <v>632</v>
+        <v>1387</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1040976831</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1040976831</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wayqe12</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -922,10 +906,10 @@
         <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="R5" t="n">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 335 6층</t>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f0zw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1169,7 +1149,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1174,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,7 +1341,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산광역시 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1366,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -624,10 +628,10 @@
         <v>1466</v>
       </c>
       <c r="Q2" t="n">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="R2" t="n">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q3" t="n">
         <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wayqe12</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 335 6층</t>
+          <t>부산 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f0zw</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1081,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1095,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>778</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1110,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1132,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1174,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1189,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>474</v>
+        <v>270</v>
       </c>
       <c r="R8" t="n">
-        <v>778</v>
+        <v>320</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1204,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1221,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1273,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w40ib3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1287,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="Q9" t="n">
-        <v>270</v>
+        <v>595</v>
       </c>
       <c r="R9" t="n">
-        <v>320</v>
+        <v>1095</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1302,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1319,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>더바른교정재활센터 해운대본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1482-1689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>http://pf.kakao.com/_pHxaws/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1361,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1372,22 +1396,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>500</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>595</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>1095</v>
+        <v>68</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1300227430</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1300227430</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -625,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="Q2" t="n">
         <v>1421</v>
       </c>
       <c r="R2" t="n">
-        <v>2887</v>
+        <v>2886</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -726,10 +726,10 @@
         <v>477</v>
       </c>
       <c r="Q3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1054,34 +1054,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>474</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>778</v>
+        <v>5</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>270</v>
+        <v>474</v>
       </c>
       <c r="R8" t="n">
-        <v>320</v>
+        <v>778</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>595</v>
+        <v>270</v>
       </c>
       <c r="R9" t="n">
-        <v>1095</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,56 +1326,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더바른교정재활센터 해운대본점</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1482-1689</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pHxaws/chat</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,33 +1385,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ib3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>595</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>1095</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1300227430</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300227430</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="35" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>1465</v>
       </c>
       <c r="Q2" t="n">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="R2" t="n">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +718,10 @@
         <v>477</v>
       </c>
       <c r="Q3" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R3" t="n">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -875,7 +863,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -900,14 +888,10 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wayqe12</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -973,7 +957,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 335 6층</t>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +982,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f0zw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1071,7 +1051,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산광역시 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1081,7 +1061,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1096,14 +1076,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>O</t>
@@ -1169,7 +1145,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1194,14 +1170,10 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1267,7 +1239,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산광역시 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1292,14 +1264,10 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1365,7 +1333,7 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산광역시 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1390,14 +1358,10 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>X</t>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -432,7 +432,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="Q2" t="n">
         <v>1422</v>
       </c>
       <c r="R2" t="n">
-        <v>2887</v>
+        <v>2889</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -675,7 +679,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +875,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
+          <t>부산 해운대구 해운대해변로 163 현대베네시티 베네치아상가 지하1층 b101호, b101-2호, b101-5호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wayqe12</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -906,10 +922,10 @@
         <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R5" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -957,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 335 6층</t>
+          <t>부산 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f0zw</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1034,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1071,18 +1091,22 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5v1em</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1091,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>474</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>778</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1170,10 +1194,14 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>474</v>
+        <v>270</v>
       </c>
       <c r="R8" t="n">
-        <v>778</v>
+        <v>320</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1264,10 +1292,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ib3</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="Q9" t="n">
-        <v>270</v>
+        <v>596</v>
       </c>
       <c r="R9" t="n">
-        <v>320</v>
+        <v>1096</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>더바른교정재활센터 해운대본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1482-1689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>http://pf.kakao.com/_pHxaws/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1353,7 +1385,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1364,22 +1396,22 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>500</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>595</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>1095</v>
+        <v>68</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1300227430</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1300227430</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로469번길 8 2층</t>
+          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5tzkb</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="Q2" t="n">
         <v>1422</v>
       </c>
       <c r="R2" t="n">
-        <v>2889</v>
+        <v>2891</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -679,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -704,14 +700,10 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4o8qo</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -726,10 +718,10 @@
         <v>477</v>
       </c>
       <c r="Q3" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="R3" t="n">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,7 +740,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -777,7 +769,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 743 4층</t>
+          <t>부산광역시 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -802,14 +794,10 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4n1kz</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -846,7 +834,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -922,10 +910,10 @@
         <v>78</v>
       </c>
       <c r="Q5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="R5" t="n">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +932,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -973,7 +961,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 335 6층</t>
+          <t>부산광역시 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -998,14 +986,10 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4f0zw</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1042,7 +1026,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1038,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1075,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1085,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1099,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>474</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>778</v>
+        <v>5</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1114,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1136,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1183,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1197,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>270</v>
+        <v>475</v>
       </c>
       <c r="R8" t="n">
-        <v>320</v>
+        <v>779</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1212,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1281,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1295,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>596</v>
+        <v>270</v>
       </c>
       <c r="R9" t="n">
-        <v>1096</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,56 +1310,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더바른교정재활센터 해운대본점</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1482-1689</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pHxaws/chat</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,33 +1369,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ib3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>596</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>1096</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1408,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1300227430</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300227430</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>마블피트니스 헬스&amp;PT 해운대점</t>
+          <t>그래비티짐 해운대 장산점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hyoyoung0202@naver.com</t>
+          <t>acmilan0@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1384-2203</t>
+          <t>0507-1397-0149</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로469번길 8 2층</t>
+          <t>부산 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hyoyoung0202</t>
+          <t>https://blog.naver.com/acmilan0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4o8qo</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1469</v>
+        <v>477</v>
       </c>
       <c r="Q2" t="n">
-        <v>1422</v>
+        <v>158</v>
       </c>
       <c r="R2" t="n">
-        <v>2891</v>
+        <v>635</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1774469002</t>
+          <t>1743697484</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1774469002</t>
+          <t>https://m.place.naver.com/place/1743697484</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>그래비티짐 해운대 장산점</t>
+          <t>마블피트니스 헬스&amp;PT 해운대점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>acmilan0@naver.com</t>
+          <t>hyoyoung0202@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1397-0149</t>
+          <t>0507-1384-2203</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 802 웅신시네아트 A동 6층</t>
+          <t>부산 해운대구 해운대로469번길 8 2층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/acmilan0</t>
+          <t>https://blog.naver.com/hyoyoung0202</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -700,10 +704,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5tzkb</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>477</v>
+        <v>1473</v>
       </c>
       <c r="Q3" t="n">
-        <v>157</v>
+        <v>1425</v>
       </c>
       <c r="R3" t="n">
-        <v>634</v>
+        <v>2898</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1743697484</t>
+          <t>1774469002</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1743697484</t>
+          <t>https://m.place.naver.com/place/1774469002</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -769,7 +777,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 743 4층</t>
+          <t>부산 해운대구 해운대로 743 4층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +802,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4n1kz</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -812,10 +824,10 @@
         <v>430</v>
       </c>
       <c r="Q4" t="n">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="R4" t="n">
-        <v>1387</v>
+        <v>1385</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -907,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q5" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="R5" t="n">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -961,7 +973,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>부산광역시 해운대구 해운대로 335 6층</t>
+          <t>부산 해운대구 해운대로 335 6층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -986,10 +998,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4f0zw</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1038,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>언로드 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>unloadpt@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1320-4232</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/s8bzzHmi</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1075,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1085,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wzjd0hu</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1099,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>304</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>476</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>780</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1114,12 +1130,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2024136684</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2024136684</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1136,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1183,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1197,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>304</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="n">
-        <v>475</v>
+        <v>270</v>
       </c>
       <c r="R8" t="n">
-        <v>779</v>
+        <v>320</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1212,12 +1228,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1229,34 +1245,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1281,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w40ib3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1295,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="Q9" t="n">
-        <v>270</v>
+        <v>598</v>
       </c>
       <c r="R9" t="n">
-        <v>320</v>
+        <v>1098</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1310,12 +1326,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1327,39 +1343,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>더바른교정재활센터 해운대본점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>j1024up@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1482-1689</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>http://pf.kakao.com/_pHxaws/chat</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1369,37 +1385,33 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>500</v>
+        <v>35</v>
       </c>
       <c r="Q10" t="n">
-        <v>596</v>
+        <v>33</v>
       </c>
       <c r="R10" t="n">
-        <v>1096</v>
+        <v>68</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1408,12 +1420,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1300227430</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1300227430</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -650,7 +650,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q5" t="n">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="R5" t="n">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>마이애미짐 센텀점 24시헬스PT</t>
+          <t>언로드 PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>miamigymnc@naver.com</t>
+          <t>unloadpt@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1319-8441</t>
+          <t>0507-1320-4232</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>부산 해운대구 센텀중앙로 90 B1</t>
+          <t>부산 해운대구 우동1로20번길 27-10 3층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/miamigymnc</t>
+          <t>https://open.kakao.com/o/s8bzzHmi</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5v1em</t>
+          <t>https://talk.naver.com/ct/wzjd0hu</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1115,13 +1115,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>304</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>476</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>780</v>
+        <v>5</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1130,17 +1130,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1160428762</t>
+          <t>2024136684</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1160428762</t>
+          <t>https://m.place.naver.com/place/2024136684</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
@@ -1152,29 +1152,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>태리짐 PT</t>
+          <t>마이애미짐 센텀점 24시헬스PT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ansth1@naver.com</t>
+          <t>miamigymnc@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1419-2400</t>
+          <t>0507-1319-8441</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
+          <t>부산 해운대구 센텀중앙로 90 B1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/ansth1</t>
+          <t>https://blog.naver.com/miamigymnc</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5ijd7</t>
+          <t>https://talk.naver.com/ct/w5v1em</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1213,13 +1213,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="Q8" t="n">
-        <v>270</v>
+        <v>476</v>
       </c>
       <c r="R8" t="n">
-        <v>320</v>
+        <v>780</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1228,51 +1228,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1346702700</t>
+          <t>1160428762</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1346702700</t>
+          <t>https://m.place.naver.com/place/1160428762</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>쑥피트니스 장산점</t>
+          <t>태리짐 PT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hgym_js2@naver.com</t>
+          <t>ansth1@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1321-1316</t>
+          <t>0507-1419-2400</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>부산 해운대구 좌동순환로 245 4층</t>
+          <t>부산 해운대구 마린시티3로 37 한일오르듀 3층 312호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/hgym_js2</t>
+          <t>https://blog.naver.com/ansth1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w40ib3</t>
+          <t>https://talk.naver.com/ct/w5ijd7</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1311,13 +1311,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="Q9" t="n">
-        <v>598</v>
+        <v>270</v>
       </c>
       <c r="R9" t="n">
-        <v>1098</v>
+        <v>320</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1326,56 +1326,56 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1198390497</t>
+          <t>1346702700</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1198390497</t>
+          <t>https://m.place.naver.com/place/1346702700</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>더바른교정재활센터 해운대본점</t>
+          <t>쑥피트니스 장산점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>j1024up@naver.com</t>
+          <t>hgym_js2@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1482-1689</t>
+          <t>0507-1321-1316</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>부산 해운대구 해운대로 794 엘리움 빌딩 3층</t>
+          <t>부산 해운대구 좌동순환로 245 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>http://pf.kakao.com/_pHxaws/chat</t>
+          <t>https://blog.naver.com/hgym_js2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1385,33 +1385,37 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w40ib3</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>35</v>
+        <v>500</v>
       </c>
       <c r="Q10" t="n">
-        <v>33</v>
+        <v>598</v>
       </c>
       <c r="R10" t="n">
-        <v>68</v>
+        <v>1098</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,17 +1424,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1300227430</t>
+          <t>1198390497</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1300227430</t>
+          <t>https://m.place.naver.com/place/1198390497</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/해운대_PT.xlsx
+++ b/naver-place-crawler/results_health/해운대_PT.xlsx
@@ -1118,10 +1118,10 @@
         <v>4</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
